--- a/open_loop_results/open_loop_margins.xlsx
+++ b/open_loop_results/open_loop_margins.xlsx
@@ -498,29 +498,21 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.983656162580111</v>
+        <v>1.975473531817015</v>
       </c>
       <c r="E2" t="n">
-        <v>86.34340070218326</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5.575953304743015</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2.180858418549319</v>
-      </c>
+        <v>85.39818961183948</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>1.983656162580111</v>
+        <v>1.975473531817015</v>
       </c>
       <c r="I2" t="n">
-        <v>86.34340070218326</v>
-      </c>
-      <c r="J2" t="n">
-        <v>5.575953304743015</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2.180858418549319</v>
-      </c>
+        <v>85.39818961183948</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -535,29 +527,21 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.504692397288691</v>
+        <v>2.646723304393497</v>
       </c>
       <c r="E3" t="n">
-        <v>53.92228210590014</v>
-      </c>
-      <c r="F3" t="n">
-        <v>6.268229360148252</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.289542594984644</v>
-      </c>
+        <v>53.63488216069807</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>2.504692397288691</v>
+        <v>2.646723304393497</v>
       </c>
       <c r="I3" t="n">
-        <v>53.92228210590014</v>
-      </c>
-      <c r="J3" t="n">
-        <v>6.268229360148252</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1.289542594984644</v>
-      </c>
+        <v>53.63488216069807</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -572,29 +556,21 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5.663692236549315</v>
+        <v>2.974890219374154</v>
       </c>
       <c r="E4" t="n">
-        <v>-22.37816833345286</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.937809058210259</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.185719753810027</v>
-      </c>
+        <v>24.7814464366198</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>5.663692236549315</v>
+        <v>2.974890219374154</v>
       </c>
       <c r="I4" t="n">
-        <v>-22.37816833345286</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.937809058210259</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1.185719753810027</v>
-      </c>
+        <v>24.7814464366198</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -609,29 +585,21 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.207437508768022</v>
+        <v>2.264853980793299</v>
       </c>
       <c r="E5" t="n">
-        <v>92.4327816142511</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5.47254565102152</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.991771958712413</v>
-      </c>
+        <v>86.45786897893485</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>1.794819064318047</v>
+        <v>1.790000509015105</v>
       </c>
       <c r="I5" t="n">
-        <v>84.58760308827311</v>
-      </c>
-      <c r="J5" t="n">
-        <v>5.248353953308387</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2.057766283018309</v>
-      </c>
+        <v>84.48370682068274</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -646,29 +614,21 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.690889736943892</v>
+        <v>2.719500711466969</v>
       </c>
       <c r="E6" t="n">
-        <v>43.20820776072716</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5.342224386612493</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.686082566407471</v>
-      </c>
+        <v>43.71319886123408</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>2.497267411290909</v>
+        <v>2.637079629380223</v>
       </c>
       <c r="I6" t="n">
-        <v>50.1735577402182</v>
-      </c>
-      <c r="J6" t="n">
-        <v>5.92415474377389</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1.616297899639003</v>
-      </c>
+        <v>48.55297423817433</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -683,29 +643,21 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3.913301952118475</v>
+        <v>3.913015022047647</v>
       </c>
       <c r="E7" t="n">
-        <v>19.51953159554571</v>
-      </c>
-      <c r="F7" t="n">
-        <v>4.911723974349684</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.405207745801256</v>
-      </c>
+        <v>19.51656588078279</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>3.265282934679349</v>
+        <v>3.235665119083912</v>
       </c>
       <c r="I7" t="n">
-        <v>33.69683831223037</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4.501696458885374</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1.578633295489108</v>
-      </c>
+        <v>33.66193972285984</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -720,29 +672,21 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.750328343652678</v>
+        <v>1.700924974346021</v>
       </c>
       <c r="E8" t="n">
-        <v>107.4357939166971</v>
-      </c>
-      <c r="F8" t="n">
-        <v>5.523597732008172</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1.91851359581593</v>
-      </c>
+        <v>107.6253066350017</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>1.750328343652678</v>
+        <v>1.700924974346021</v>
       </c>
       <c r="I8" t="n">
-        <v>107.4357939166971</v>
-      </c>
-      <c r="J8" t="n">
-        <v>5.523597732008172</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1.91851359581593</v>
-      </c>
+        <v>107.6253066350017</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -757,29 +701,21 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.809284641259806</v>
+        <v>1.794673715158993</v>
       </c>
       <c r="E9" t="n">
-        <v>62.62620577429351</v>
-      </c>
-      <c r="F9" t="n">
-        <v>5.222446503113457</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.758166691265139</v>
-      </c>
+        <v>62.71398471056857</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>1.809284641259806</v>
+        <v>1.794673715158993</v>
       </c>
       <c r="I9" t="n">
-        <v>62.62620577429351</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.222446503113457</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.758166691265139</v>
-      </c>
+        <v>62.71398471056857</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -794,29 +730,21 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.767225144934416</v>
+        <v>1.795299898210109</v>
       </c>
       <c r="E10" t="n">
-        <v>34.28515200334513</v>
-      </c>
-      <c r="F10" t="n">
-        <v>4.018166596030831</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.935192899451827</v>
-      </c>
+        <v>33.81630371875951</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>1.767225144934416</v>
+        <v>1.795299898210109</v>
       </c>
       <c r="I10" t="n">
-        <v>34.28515200334513</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4.018166596030831</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.935192899451827</v>
-      </c>
+        <v>33.81630371875951</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -831,29 +759,21 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.917022560858407</v>
+        <v>1.892747956862609</v>
       </c>
       <c r="E11" t="n">
-        <v>100.3992309338429</v>
-      </c>
-      <c r="F11" t="n">
-        <v>5.960917392231902</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2.882605749935861</v>
-      </c>
+        <v>101.0733128459403</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>1.089460164733649</v>
+        <v>1.163366017569644</v>
       </c>
       <c r="I11" t="n">
-        <v>105.5800513286205</v>
-      </c>
-      <c r="J11" t="n">
-        <v>5.283465265169139</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1.993942268305979</v>
-      </c>
+        <v>103.4073627366528</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -868,29 +788,21 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.008555673115271</v>
+        <v>1.993758598366007</v>
       </c>
       <c r="E12" t="n">
-        <v>71.72210398163884</v>
-      </c>
-      <c r="F12" t="n">
-        <v>6.378659646694374</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2.410726310243919</v>
-      </c>
+        <v>71.5642636611948</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>1.098208499051803</v>
+        <v>1.165517069432892</v>
       </c>
       <c r="I12" t="n">
-        <v>75.14295211423439</v>
-      </c>
-      <c r="J12" t="n">
-        <v>5.230295539014442</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2.353204783476282</v>
-      </c>
+        <v>73.50780703357547</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -905,29 +817,21 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.928942332701703</v>
+        <v>2.922891786330172</v>
       </c>
       <c r="E13" t="n">
-        <v>25.96669418099458</v>
-      </c>
-      <c r="F13" t="n">
-        <v>4.892040425885963</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.761443915470629</v>
-      </c>
+        <v>25.49444825156331</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>1.946402081953237</v>
+        <v>1.92118418190901</v>
       </c>
       <c r="I13" t="n">
-        <v>51.35211482285416</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4.271484122121592</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1.908642868439535</v>
-      </c>
+        <v>51.56669372114206</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -942,29 +846,21 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.6108785454134</v>
+        <v>1.41076920037148</v>
       </c>
       <c r="E14" t="n">
-        <v>84.47883500785133</v>
-      </c>
-      <c r="F14" t="n">
-        <v>4.530594405036823</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.02658602871501</v>
-      </c>
+        <v>90.44649198022796</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>1.6108785454134</v>
+        <v>1.41076920037148</v>
       </c>
       <c r="I14" t="n">
-        <v>84.47883500785133</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4.530594405036823</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2.02658602871501</v>
-      </c>
+        <v>90.44649198022796</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -979,29 +875,21 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2.578359313951552</v>
+        <v>2.535846012278861</v>
       </c>
       <c r="E15" t="n">
-        <v>45.91550903754001</v>
-      </c>
-      <c r="F15" t="n">
-        <v>4.686852395469432</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.109769360761757</v>
-      </c>
+        <v>48.33223211598511</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>2.578359313951552</v>
+        <v>2.535846012278861</v>
       </c>
       <c r="I15" t="n">
-        <v>45.91550903754001</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4.686852395469432</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1.109769360761757</v>
-      </c>
+        <v>48.33223211598511</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1016,29 +904,21 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2.080859551441862</v>
+        <v>2.121469186808064</v>
       </c>
       <c r="E16" t="n">
-        <v>19.75615714398339</v>
-      </c>
-      <c r="F16" t="n">
-        <v>3.834094846857954</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1.684266412964379</v>
-      </c>
+        <v>379.2000990850913</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>2.080859551441862</v>
+        <v>2.121469186808064</v>
       </c>
       <c r="I16" t="n">
-        <v>19.75615714398339</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.834094846857954</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1.684266412964379</v>
-      </c>
+        <v>379.2000990850913</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1053,29 +933,21 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.927254113251412</v>
+        <v>1.915990107705932</v>
       </c>
       <c r="E17" t="n">
-        <v>79.17779787359626</v>
-      </c>
-      <c r="F17" t="n">
-        <v>6.468675683618368</v>
-      </c>
-      <c r="G17" t="n">
-        <v>4.106502431057597</v>
-      </c>
+        <v>79.68533573069855</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>1.704372175462322</v>
+        <v>1.675886180257961</v>
       </c>
       <c r="I17" t="n">
-        <v>79.40220741424696</v>
-      </c>
-      <c r="J17" t="n">
-        <v>5.616258236940272</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1.800522952330169</v>
-      </c>
+        <v>79.78903499425263</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1090,29 +962,21 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.033308433501719</v>
+        <v>2.028646685722211</v>
       </c>
       <c r="E18" t="n">
-        <v>51.47560354030122</v>
-      </c>
-      <c r="F18" t="n">
-        <v>6.945993569054916</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3.281863911736651</v>
-      </c>
+        <v>51.45787470653724</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>1.6768532333226</v>
+        <v>1.68422666422796</v>
       </c>
       <c r="I18" t="n">
-        <v>59.87675005688385</v>
-      </c>
-      <c r="J18" t="n">
-        <v>5.314336690442683</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2.083884716626385</v>
-      </c>
+        <v>59.86045512756998</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1127,29 +991,21 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.320506507544616</v>
+        <v>2.336932161676698</v>
       </c>
       <c r="E19" t="n">
-        <v>32.2891739710908</v>
-      </c>
-      <c r="F19" t="n">
-        <v>5.638030620240725</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3.649439967437078</v>
-      </c>
+        <v>31.53268412054928</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>1.942969641429979</v>
+        <v>1.920025108620212</v>
       </c>
       <c r="I19" t="n">
-        <v>35.71517051800149</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3.476403944818601</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2.126900417353205</v>
-      </c>
+        <v>35.67173269194737</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1164,29 +1020,21 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.76811830415707</v>
+        <v>2.74080004836852</v>
       </c>
       <c r="E20" t="n">
-        <v>57.01777863390834</v>
-      </c>
-      <c r="F20" t="n">
-        <v>5.472963775200987</v>
-      </c>
-      <c r="G20" t="n">
-        <v>2.094392398280628</v>
-      </c>
+        <v>57.65673369893727</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>2.76811830415707</v>
+        <v>2.74080004836852</v>
       </c>
       <c r="I20" t="n">
-        <v>57.01777863390834</v>
-      </c>
-      <c r="J20" t="n">
-        <v>5.472963775200987</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2.094392398280628</v>
-      </c>
+        <v>57.65673369893727</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1201,29 +1049,21 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2.039897144752146</v>
+        <v>2.038925422586108</v>
       </c>
       <c r="E21" t="n">
-        <v>64.6867879409491</v>
-      </c>
-      <c r="F21" t="n">
-        <v>7.56511040169458</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2.508244181454529</v>
-      </c>
+        <v>64.31430036122065</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>2.039897144752146</v>
+        <v>2.038925422586108</v>
       </c>
       <c r="I21" t="n">
-        <v>64.6867879409491</v>
-      </c>
-      <c r="J21" t="n">
-        <v>7.56511040169458</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2.508244181454529</v>
-      </c>
+        <v>64.31430036122065</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1238,29 +1078,21 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2.199182149022298</v>
+        <v>2.215322031492847</v>
       </c>
       <c r="E22" t="n">
-        <v>18.40504632753215</v>
-      </c>
-      <c r="F22" t="n">
-        <v>4.900548437645305</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1.40287244518519</v>
-      </c>
+        <v>380.0662043257428</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>2.199182149022298</v>
+        <v>2.215322031492847</v>
       </c>
       <c r="I22" t="n">
-        <v>18.40504632753215</v>
-      </c>
-      <c r="J22" t="n">
-        <v>4.900548437645305</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1.40287244518519</v>
-      </c>
+        <v>380.0662043257428</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1275,29 +1107,21 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2.399659245409984</v>
+        <v>2.439587249185493</v>
       </c>
       <c r="E23" t="n">
-        <v>61.10949867329833</v>
-      </c>
-      <c r="F23" t="n">
-        <v>6.46795086994171</v>
-      </c>
-      <c r="G23" t="n">
-        <v>4.159944586681004</v>
-      </c>
+        <v>58.66651700453572</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>1.91111020471144</v>
+        <v>1.900866327848026</v>
       </c>
       <c r="I23" t="n">
-        <v>71.16333751140655</v>
-      </c>
-      <c r="J23" t="n">
-        <v>5.527601143399226</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1.925815948689485</v>
-      </c>
+        <v>70.54109912537405</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1312,29 +1136,21 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2.890559630690709</v>
+        <v>2.889769483121692</v>
       </c>
       <c r="E24" t="n">
-        <v>39.26624213812315</v>
-      </c>
-      <c r="F24" t="n">
-        <v>6.337239443725433</v>
-      </c>
-      <c r="G24" t="n">
-        <v>2.010796163888479</v>
-      </c>
+        <v>39.59508514456704</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>1.990699746845968</v>
+        <v>1.98141793526696</v>
       </c>
       <c r="I24" t="n">
-        <v>58.00264728976646</v>
-      </c>
-      <c r="J24" t="n">
-        <v>5.791034036209719</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1.857379988379033</v>
-      </c>
+        <v>57.81702624200189</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1349,29 +1165,21 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2.706103237312254</v>
+        <v>2.702353198656887</v>
       </c>
       <c r="E25" t="n">
-        <v>22.28004989511501</v>
-      </c>
-      <c r="F25" t="n">
-        <v>4.956589511405915</v>
-      </c>
-      <c r="G25" t="n">
-        <v>2.253161191110475</v>
-      </c>
+        <v>382.9995968134995</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>1.926367880215745</v>
+        <v>1.898631026680534</v>
       </c>
       <c r="I25" t="n">
-        <v>52.58349709015607</v>
-      </c>
-      <c r="J25" t="n">
-        <v>4.350775204915785</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2.431529314233762</v>
-      </c>
+        <v>52.40012863987752</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1386,29 +1194,21 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2.04507299055068</v>
+        <v>2.045174000628029</v>
       </c>
       <c r="E26" t="n">
-        <v>86.7767390853399</v>
-      </c>
-      <c r="F26" t="n">
-        <v>5.581891006151387</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1.632516762944474</v>
-      </c>
+        <v>86.0905402497752</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>2.04507299055068</v>
+        <v>2.045174000628029</v>
       </c>
       <c r="I26" t="n">
-        <v>86.7767390853399</v>
-      </c>
-      <c r="J26" t="n">
-        <v>5.581891006151387</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1.632516762944474</v>
-      </c>
+        <v>86.0905402497752</v>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1423,29 +1223,21 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1.943212972044229</v>
+        <v>1.931124990708419</v>
       </c>
       <c r="E27" t="n">
-        <v>72.89399338570922</v>
-      </c>
-      <c r="F27" t="n">
-        <v>4.758548812086566</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1.322568308718473</v>
-      </c>
+        <v>72.04892138967101</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>1.943212972044229</v>
+        <v>1.931124990708419</v>
       </c>
       <c r="I27" t="n">
-        <v>72.89399338570922</v>
-      </c>
-      <c r="J27" t="n">
-        <v>4.758548812086566</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1.322568308718473</v>
-      </c>
+        <v>72.04892138967101</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1460,29 +1252,21 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2.647653693155355</v>
+        <v>2.477582878890399</v>
       </c>
       <c r="E28" t="n">
-        <v>15.68964395817392</v>
-      </c>
-      <c r="F28" t="n">
-        <v>4.223512937974741</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1.429827632062084</v>
-      </c>
+        <v>389.0924066176296</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>2.647653693155355</v>
+        <v>2.477582878890399</v>
       </c>
       <c r="I28" t="n">
-        <v>15.68964395817392</v>
-      </c>
-      <c r="J28" t="n">
-        <v>4.223512937974741</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1.429827632062084</v>
-      </c>
+        <v>389.0924066176296</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1497,29 +1281,21 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2.553799261844229</v>
+        <v>2.580056985351093</v>
       </c>
       <c r="E29" t="n">
-        <v>71.16601583258182</v>
-      </c>
-      <c r="F29" t="n">
-        <v>6.419400342465533</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1.760796356110362</v>
-      </c>
+        <v>69.13699474302103</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>2.562574932353603</v>
+        <v>2.562886774990454</v>
       </c>
       <c r="I29" t="n">
-        <v>52.5213078890165</v>
-      </c>
-      <c r="J29" t="n">
-        <v>5.609627085439079</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1.486094994813412</v>
-      </c>
+        <v>53.33677334027311</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1534,29 +1310,21 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2.844637962965334</v>
+        <v>2.845447291833321</v>
       </c>
       <c r="E30" t="n">
-        <v>51.44841191707482</v>
-      </c>
-      <c r="F30" t="n">
-        <v>6.583068889731217</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1.949198689073097</v>
-      </c>
+        <v>51.50744252903431</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>1.907207363149277</v>
+        <v>1.895928311527037</v>
       </c>
       <c r="I30" t="n">
-        <v>63.16664465207998</v>
-      </c>
-      <c r="J30" t="n">
-        <v>10.45035502562554</v>
-      </c>
-      <c r="K30" t="n">
-        <v>1.239604852732112</v>
-      </c>
+        <v>63.11217677393483</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1571,29 +1339,21 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3.26947747806847</v>
+        <v>3.303601863102024</v>
       </c>
       <c r="E31" t="n">
-        <v>19.54399712293576</v>
-      </c>
-      <c r="F31" t="n">
-        <v>5.342612383428056</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1.695940564568573</v>
-      </c>
+        <v>20.61572410704457</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>2.165370345999443</v>
+        <v>2.257744011677711</v>
       </c>
       <c r="I31" t="n">
-        <v>46.15650464678117</v>
-      </c>
-      <c r="J31" t="n">
-        <v>4.431666826861323</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2.039454854830266</v>
-      </c>
+        <v>43.95012446737448</v>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1609,20 +1369,12 @@
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
-        <v>6.090015575201476</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1.451312436108175</v>
-      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="n">
-        <v>6.090015575201476</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1.451312436108175</v>
-      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1637,29 +1389,21 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2.22785989458201</v>
+        <v>2.279675077663983</v>
       </c>
       <c r="E33" t="n">
-        <v>64.1596587318665</v>
-      </c>
-      <c r="F33" t="n">
-        <v>4.55255798604365</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.9846777821420708</v>
-      </c>
+        <v>65.38889657090716</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>2.22785989458201</v>
+        <v>2.279675077663983</v>
       </c>
       <c r="I33" t="n">
-        <v>64.1596587318665</v>
-      </c>
-      <c r="J33" t="n">
-        <v>4.55255798604365</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.9846777821420708</v>
-      </c>
+        <v>65.38889657090716</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1674,29 +1418,21 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.166074854239215</v>
+        <v>2.181180175293617</v>
       </c>
       <c r="E34" t="n">
-        <v>20.5802264640503</v>
-      </c>
-      <c r="F34" t="n">
-        <v>3.938862970946678</v>
-      </c>
-      <c r="G34" t="n">
-        <v>2.058094165690778</v>
-      </c>
+        <v>22.16193241227458</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>2.166074854239215</v>
+        <v>2.181180175293617</v>
       </c>
       <c r="I34" t="n">
-        <v>20.5802264640503</v>
-      </c>
-      <c r="J34" t="n">
-        <v>3.938862970946678</v>
-      </c>
-      <c r="K34" t="n">
-        <v>2.058094165690778</v>
-      </c>
+        <v>22.16193241227458</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1711,29 +1447,21 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1.531427322911027</v>
+        <v>1.464181185363502</v>
       </c>
       <c r="E35" t="n">
-        <v>103.9891803670715</v>
-      </c>
-      <c r="F35" t="n">
-        <v>6.682555737876917</v>
-      </c>
-      <c r="G35" t="n">
-        <v>3.530198894354658</v>
-      </c>
+        <v>104.2661125035755</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>1.10001956795352</v>
+        <v>1.182668375645899</v>
       </c>
       <c r="I35" t="n">
-        <v>93.17439288039759</v>
-      </c>
-      <c r="J35" t="n">
-        <v>5.356175638020702</v>
-      </c>
-      <c r="K35" t="n">
-        <v>2.039837957796733</v>
-      </c>
+        <v>91.69227472504178</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1748,29 +1476,21 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2.281715486734926</v>
+        <v>2.324719045367077</v>
       </c>
       <c r="E36" t="n">
-        <v>67.29965329910391</v>
-      </c>
-      <c r="F36" t="n">
-        <v>6.316220213535926</v>
-      </c>
-      <c r="G36" t="n">
-        <v>2.022285006062282</v>
-      </c>
+        <v>66.37439512659783</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>1.40300197717187</v>
+        <v>1.458704218630605</v>
       </c>
       <c r="I36" t="n">
-        <v>73.19639036575558</v>
-      </c>
-      <c r="J36" t="n">
-        <v>5.437697187910097</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2.058392060838436</v>
-      </c>
+        <v>69.83664771140226</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1785,29 +1505,21 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2.975163547127258</v>
+        <v>2.96736952611436</v>
       </c>
       <c r="E37" t="n">
-        <v>23.58415492394948</v>
-      </c>
-      <c r="F37" t="n">
-        <v>5.399879228899986</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1.896678899645108</v>
-      </c>
+        <v>23.13553055760431</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>1.853163284648526</v>
+        <v>1.82670999976919</v>
       </c>
       <c r="I37" t="n">
-        <v>52.35218377781695</v>
-      </c>
-      <c r="J37" t="n">
-        <v>4.326258316714536</v>
-      </c>
-      <c r="K37" t="n">
-        <v>2.104569749609697</v>
-      </c>
+        <v>52.66675922890093</v>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/open_loop_results/open_loop_margins.xlsx
+++ b/open_loop_results/open_loop_margins.xlsx
@@ -501,7 +501,7 @@
         <v>1.975473531817015</v>
       </c>
       <c r="E2" t="n">
-        <v>85.39818961183948</v>
+        <v>85.3981896118395</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -509,7 +509,7 @@
         <v>1.975473531817015</v>
       </c>
       <c r="I2" t="n">
-        <v>85.39818961183948</v>
+        <v>85.3981896118395</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -527,18 +527,18 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.646723304393497</v>
+        <v>2.646723307567413</v>
       </c>
       <c r="E3" t="n">
-        <v>53.63488216069807</v>
+        <v>53.6348831094048</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>2.646723304393497</v>
+        <v>2.646723307567413</v>
       </c>
       <c r="I3" t="n">
-        <v>53.63488216069807</v>
+        <v>53.6348831094048</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -588,7 +588,7 @@
         <v>2.264853980793299</v>
       </c>
       <c r="E5" t="n">
-        <v>86.45786897893485</v>
+        <v>86.45786897893484</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -596,7 +596,7 @@
         <v>1.790000509015105</v>
       </c>
       <c r="I5" t="n">
-        <v>84.48370682068274</v>
+        <v>84.48370682068273</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -614,18 +614,18 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.719500711466969</v>
+        <v>2.719500715363603</v>
       </c>
       <c r="E6" t="n">
-        <v>43.71319886123408</v>
+        <v>43.71319982806091</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>2.637079629380223</v>
+        <v>2.637079633217062</v>
       </c>
       <c r="I6" t="n">
-        <v>48.55297423817433</v>
+        <v>48.55297526496946</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -701,18 +701,18 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.794673715158993</v>
+        <v>1.794673715848276</v>
       </c>
       <c r="E9" t="n">
-        <v>62.71398471056857</v>
+        <v>62.71398538926992</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>1.794673715158993</v>
+        <v>1.794673715848276</v>
       </c>
       <c r="I9" t="n">
-        <v>62.71398471056857</v>
+        <v>62.71398538926992</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -770,7 +770,7 @@
         <v>1.163366017569644</v>
       </c>
       <c r="I11" t="n">
-        <v>103.4073627366528</v>
+        <v>103.4073627366529</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -788,18 +788,18 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.993758598366007</v>
+        <v>1.993758599495327</v>
       </c>
       <c r="E12" t="n">
-        <v>71.5642636611948</v>
+        <v>71.56426441593251</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>1.165517069432892</v>
+        <v>1.165517067313956</v>
       </c>
       <c r="I12" t="n">
-        <v>73.50780703357547</v>
+        <v>73.50780742979623</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -875,18 +875,18 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2.535846012278861</v>
+        <v>2.535846016165929</v>
       </c>
       <c r="E15" t="n">
-        <v>48.33223211598511</v>
+        <v>48.33223303707018</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>2.535846012278861</v>
+        <v>2.535846016165929</v>
       </c>
       <c r="I15" t="n">
-        <v>48.33223211598511</v>
+        <v>48.33223303707018</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -962,18 +962,18 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.028646685722211</v>
+        <v>2.028646687228788</v>
       </c>
       <c r="E18" t="n">
-        <v>51.45787470653724</v>
+        <v>51.45787546373109</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>1.68422666422796</v>
+        <v>1.684226660587159</v>
       </c>
       <c r="I18" t="n">
-        <v>59.86045512756998</v>
+        <v>59.86045576786044</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1049,18 +1049,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2.038925422586108</v>
+        <v>2.038925425079407</v>
       </c>
       <c r="E21" t="n">
-        <v>64.31430036122065</v>
+        <v>64.314301037086</v>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>2.038925422586108</v>
+        <v>2.038925425079407</v>
       </c>
       <c r="I21" t="n">
-        <v>64.31430036122065</v>
+        <v>64.314301037086</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1110,7 +1110,7 @@
         <v>2.439587249185493</v>
       </c>
       <c r="E23" t="n">
-        <v>58.66651700453572</v>
+        <v>58.66651700453571</v>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
@@ -1136,18 +1136,18 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2.889769483121692</v>
+        <v>2.889769488893627</v>
       </c>
       <c r="E24" t="n">
-        <v>39.59508514456704</v>
+        <v>39.59508627668617</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>1.98141793526696</v>
+        <v>1.981417927256623</v>
       </c>
       <c r="I24" t="n">
-        <v>57.81702624200189</v>
+        <v>57.81702691109842</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -1223,18 +1223,18 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1.931124990708419</v>
+        <v>1.931124991618978</v>
       </c>
       <c r="E27" t="n">
-        <v>72.04892138967101</v>
+        <v>72.04892208840809</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>1.931124990708419</v>
+        <v>1.931124991618978</v>
       </c>
       <c r="I27" t="n">
-        <v>72.04892138967101</v>
+        <v>72.04892208840809</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -1284,7 +1284,7 @@
         <v>2.580056985351093</v>
       </c>
       <c r="E29" t="n">
-        <v>69.13699474302103</v>
+        <v>69.13699474302101</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
@@ -1310,18 +1310,18 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2.845447291833321</v>
+        <v>2.845447299373791</v>
       </c>
       <c r="E30" t="n">
-        <v>51.50744252903431</v>
+        <v>51.50744361526105</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>1.895928311527037</v>
+        <v>1.895928309579628</v>
       </c>
       <c r="I30" t="n">
-        <v>63.11217677393483</v>
+        <v>63.11217729956573</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -1389,18 +1389,18 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2.279675077663983</v>
+        <v>2.279675081093558</v>
       </c>
       <c r="E33" t="n">
-        <v>65.38889657090716</v>
+        <v>65.38889740593375</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>2.279675077663983</v>
+        <v>2.279675081093558</v>
       </c>
       <c r="I33" t="n">
-        <v>65.38889657090716</v>
+        <v>65.38889740593375</v>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -1476,18 +1476,18 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2.324719045367077</v>
+        <v>2.324719049755511</v>
       </c>
       <c r="E36" t="n">
-        <v>66.37439512659783</v>
+        <v>66.37439595824624</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>1.458704218630605</v>
+        <v>1.458704217559575</v>
       </c>
       <c r="I36" t="n">
-        <v>69.83664771140226</v>
+        <v>69.83664815224265</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>

--- a/open_loop_results/open_loop_margins.xlsx
+++ b/open_loop_results/open_loop_margins.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,57 +417,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>subject</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>condition_name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>disturbance_gain_crossover_rad_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>disturbance_phase_margin_deg</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>disturbance_phase_crossover_rad_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>disturbance_gain_margin</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>target_gain_crossover_rad_s</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>target_phase_margin_deg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>target_phase_crossover_rad_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>target_gain_margin</t>
         </is>
@@ -1020,18 +1008,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.74080004836852</v>
+        <v>2.740800048368519</v>
       </c>
       <c r="E20" t="n">
-        <v>57.65673369893727</v>
+        <v>57.65673369893729</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>2.74080004836852</v>
+        <v>2.740800048368519</v>
       </c>
       <c r="I20" t="n">
-        <v>57.65673369893727</v>
+        <v>57.65673369893729</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1284,7 +1272,7 @@
         <v>2.580056985351093</v>
       </c>
       <c r="E29" t="n">
-        <v>69.13699474302101</v>
+        <v>69.13699474302103</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
@@ -1350,7 +1338,7 @@
         <v>2.257744011677711</v>
       </c>
       <c r="I31" t="n">
-        <v>43.95012446737448</v>
+        <v>43.95012446737451</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1508,7 +1496,7 @@
         <v>2.96736952611436</v>
       </c>
       <c r="E37" t="n">
-        <v>23.13553055760431</v>
+        <v>23.13553055760434</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>

--- a/open_loop_results/open_loop_margins.xlsx
+++ b/open_loop_results/open_loop_margins.xlsx
@@ -895,7 +895,7 @@
         <v>2.121469186808064</v>
       </c>
       <c r="E16" t="n">
-        <v>379.2000990850913</v>
+        <v>19.20009908509132</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
@@ -903,7 +903,7 @@
         <v>2.121469186808064</v>
       </c>
       <c r="I16" t="n">
-        <v>379.2000990850913</v>
+        <v>19.20009908509132</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1069,7 +1069,7 @@
         <v>2.215322031492847</v>
       </c>
       <c r="E22" t="n">
-        <v>380.0662043257428</v>
+        <v>20.06620432574283</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
         <v>2.215322031492847</v>
       </c>
       <c r="I22" t="n">
-        <v>380.0662043257428</v>
+        <v>20.06620432574283</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -1156,7 +1156,7 @@
         <v>2.702353198656887</v>
       </c>
       <c r="E25" t="n">
-        <v>382.9995968134995</v>
+        <v>22.99959681349947</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
         <v>2.477582878890399</v>
       </c>
       <c r="E28" t="n">
-        <v>389.0924066176296</v>
+        <v>29.09240661762965</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
@@ -1251,7 +1251,7 @@
         <v>2.477582878890399</v>
       </c>
       <c r="I28" t="n">
-        <v>389.0924066176296</v>
+        <v>29.09240661762965</v>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
